--- a/history_prices/JULY/prices_01072026.xlsx
+++ b/history_prices/JULY/prices_01072026.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\history_prices\JULY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD465259-9288-4B27-816D-E9C777723797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46A159D-3F23-4F59-8C34-182C63E117F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ЕКО БЮЛЕТИН" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="477">
   <si>
     <t>ID</t>
   </si>
@@ -1436,6 +1436,21 @@
   </si>
   <si>
     <t>0414</t>
+  </si>
+  <si>
+    <t>ТРАКИЙСКИ УНИВЕРСИТЕТ</t>
+  </si>
+  <si>
+    <t>ТРАКИЙСКИ  УНИВЕРСИТЕТ % 1 - ФИЛИАЛ ГР. ХАСКОВО</t>
+  </si>
+  <si>
+    <t>ТРАКИЙСКИ  УНИВЕРСИТЕТ % 2 - ФАКУЛТЕТ ТЕХНИКА И ТЕХНОЛОГИИ</t>
+  </si>
+  <si>
+    <t>ТРАКИЙСКИ  УНИВЕРСИТЕТ % 3 - РЕКТОРАТ</t>
+  </si>
+  <si>
+    <t>ТРАКИЙСКИ  УНИВЕРСИТЕТ % 4 - АКАДЕМИЧЕН ТЕХНОЛОГИЧЕН КОМПЛЕКС</t>
   </si>
 </sst>
 </file>
@@ -1443,9 +1458,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="&quot;€&quot;#,##0.00_-"/>
-    <numFmt numFmtId="167" formatCode="&quot;€&quot;#,##0.000_-"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="&quot;€&quot;#,##0.00_-"/>
+    <numFmt numFmtId="166" formatCode="&quot;€&quot;#,##0.000_-"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -1476,11 +1491,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1783,19 +1804,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O270"/>
+  <dimension ref="A1:O285"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" customWidth="1"/>
     <col min="2" max="2" width="23.28515625" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="23.28515625" customWidth="1"/>
+    <col min="4" max="4" width="70.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.42578125" customWidth="1"/>
     <col min="6" max="7" width="23.28515625" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="28.140625" customWidth="1"/>
     <col min="10" max="10" width="27.42578125" customWidth="1"/>
-    <col min="11" max="15" width="23.28515625" customWidth="1"/>
+    <col min="11" max="14" width="23.28515625" customWidth="1"/>
+    <col min="15" max="15" width="25.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -10753,6 +10775,9 @@
       <c r="G266" s="3">
         <v>1</v>
       </c>
+      <c r="H266" s="3">
+        <v>0</v>
+      </c>
       <c r="I266" s="2">
         <v>1</v>
       </c>
@@ -10898,6 +10923,455 @@
       </c>
       <c r="O270" t="s">
         <v>470</v>
+      </c>
+    </row>
+    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B271" t="s">
+        <v>5</v>
+      </c>
+      <c r="C271" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D271" t="s">
+        <v>472</v>
+      </c>
+      <c r="E271" t="s">
+        <v>17</v>
+      </c>
+      <c r="F271" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G271" s="3">
+        <v>1.399</v>
+      </c>
+      <c r="H271" s="3">
+        <v>0</v>
+      </c>
+      <c r="I271" s="2">
+        <v>1.43</v>
+      </c>
+      <c r="O271" s="4">
+        <v>123024538</v>
+      </c>
+    </row>
+    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B272" t="s">
+        <v>5</v>
+      </c>
+      <c r="C272" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D272" t="s">
+        <v>472</v>
+      </c>
+      <c r="E272" t="s">
+        <v>22</v>
+      </c>
+      <c r="F272" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G272" s="3">
+        <v>1.359</v>
+      </c>
+      <c r="H272" s="3">
+        <v>0</v>
+      </c>
+      <c r="I272" s="2">
+        <f>F272+G272</f>
+        <v>1.389</v>
+      </c>
+      <c r="O272" s="4">
+        <v>123024538</v>
+      </c>
+    </row>
+    <row r="273" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B273" t="s">
+        <v>5</v>
+      </c>
+      <c r="C273" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D273" t="s">
+        <v>472</v>
+      </c>
+      <c r="E273" t="s">
+        <v>71</v>
+      </c>
+      <c r="F273" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G273" s="3">
+        <v>1.619</v>
+      </c>
+      <c r="H273" s="3">
+        <v>0</v>
+      </c>
+      <c r="I273" s="2">
+        <f>F273+G273</f>
+        <v>1.649</v>
+      </c>
+      <c r="O273" s="4">
+        <v>123024538</v>
+      </c>
+    </row>
+    <row r="274" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B274" t="s">
+        <v>5</v>
+      </c>
+      <c r="C274" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D274" t="s">
+        <v>473</v>
+      </c>
+      <c r="E274" t="s">
+        <v>17</v>
+      </c>
+      <c r="F274" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G274" s="3">
+        <v>1.399</v>
+      </c>
+      <c r="H274" s="3">
+        <v>0</v>
+      </c>
+      <c r="I274" s="2">
+        <f t="shared" ref="I274:I285" si="0">F274+G274</f>
+        <v>1.429</v>
+      </c>
+      <c r="O274" s="4">
+        <v>123024538</v>
+      </c>
+    </row>
+    <row r="275" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B275" t="s">
+        <v>5</v>
+      </c>
+      <c r="C275" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D275" t="s">
+        <v>473</v>
+      </c>
+      <c r="E275" t="s">
+        <v>22</v>
+      </c>
+      <c r="F275" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G275" s="3">
+        <v>1.359</v>
+      </c>
+      <c r="H275" s="3">
+        <v>0</v>
+      </c>
+      <c r="I275" s="2">
+        <f t="shared" si="0"/>
+        <v>1.389</v>
+      </c>
+      <c r="O275" s="4">
+        <v>123024538</v>
+      </c>
+    </row>
+    <row r="276" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B276" t="s">
+        <v>5</v>
+      </c>
+      <c r="C276" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D276" t="s">
+        <v>473</v>
+      </c>
+      <c r="E276" t="s">
+        <v>71</v>
+      </c>
+      <c r="F276" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G276" s="3">
+        <v>1.619</v>
+      </c>
+      <c r="H276" s="3">
+        <v>0</v>
+      </c>
+      <c r="I276" s="2">
+        <f t="shared" si="0"/>
+        <v>1.649</v>
+      </c>
+      <c r="O276" s="4">
+        <v>123024538</v>
+      </c>
+    </row>
+    <row r="277" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B277" t="s">
+        <v>5</v>
+      </c>
+      <c r="C277" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D277" t="s">
+        <v>474</v>
+      </c>
+      <c r="E277" t="s">
+        <v>17</v>
+      </c>
+      <c r="F277" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G277" s="3">
+        <v>1.399</v>
+      </c>
+      <c r="H277" s="3">
+        <v>0</v>
+      </c>
+      <c r="I277" s="2">
+        <f t="shared" si="0"/>
+        <v>1.429</v>
+      </c>
+      <c r="O277" s="5">
+        <v>1230245380127</v>
+      </c>
+    </row>
+    <row r="278" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B278" t="s">
+        <v>5</v>
+      </c>
+      <c r="C278" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D278" t="s">
+        <v>474</v>
+      </c>
+      <c r="E278" t="s">
+        <v>22</v>
+      </c>
+      <c r="F278" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G278" s="3">
+        <v>1.359</v>
+      </c>
+      <c r="H278" s="3">
+        <v>0</v>
+      </c>
+      <c r="I278" s="2">
+        <f t="shared" si="0"/>
+        <v>1.389</v>
+      </c>
+      <c r="O278" s="5">
+        <v>1230245380127</v>
+      </c>
+    </row>
+    <row r="279" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B279" t="s">
+        <v>5</v>
+      </c>
+      <c r="C279" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D279" t="s">
+        <v>474</v>
+      </c>
+      <c r="E279" t="s">
+        <v>71</v>
+      </c>
+      <c r="F279" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G279" s="3">
+        <v>1.619</v>
+      </c>
+      <c r="H279" s="3">
+        <v>0</v>
+      </c>
+      <c r="I279" s="2">
+        <f t="shared" si="0"/>
+        <v>1.649</v>
+      </c>
+      <c r="O279" s="5">
+        <v>1230245380127</v>
+      </c>
+    </row>
+    <row r="280" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B280" t="s">
+        <v>5</v>
+      </c>
+      <c r="C280" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D280" t="s">
+        <v>475</v>
+      </c>
+      <c r="E280" t="s">
+        <v>17</v>
+      </c>
+      <c r="F280" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G280" s="3">
+        <v>1.399</v>
+      </c>
+      <c r="H280" s="3">
+        <v>0</v>
+      </c>
+      <c r="I280" s="2">
+        <f t="shared" si="0"/>
+        <v>1.429</v>
+      </c>
+      <c r="O280" s="4">
+        <v>123024538</v>
+      </c>
+    </row>
+    <row r="281" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B281" t="s">
+        <v>5</v>
+      </c>
+      <c r="C281" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D281" t="s">
+        <v>475</v>
+      </c>
+      <c r="E281" t="s">
+        <v>22</v>
+      </c>
+      <c r="F281" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G281" s="3">
+        <v>1.359</v>
+      </c>
+      <c r="H281" s="3">
+        <v>0</v>
+      </c>
+      <c r="I281" s="2">
+        <f t="shared" si="0"/>
+        <v>1.389</v>
+      </c>
+      <c r="O281" s="4">
+        <v>123024538</v>
+      </c>
+    </row>
+    <row r="282" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B282" t="s">
+        <v>5</v>
+      </c>
+      <c r="C282" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D282" t="s">
+        <v>475</v>
+      </c>
+      <c r="E282" t="s">
+        <v>71</v>
+      </c>
+      <c r="F282" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G282" s="3">
+        <v>1.619</v>
+      </c>
+      <c r="H282" s="3">
+        <v>0</v>
+      </c>
+      <c r="I282" s="2">
+        <f t="shared" si="0"/>
+        <v>1.649</v>
+      </c>
+      <c r="O282" s="4">
+        <v>123024538</v>
+      </c>
+    </row>
+    <row r="283" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B283" t="s">
+        <v>5</v>
+      </c>
+      <c r="C283" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D283" t="s">
+        <v>476</v>
+      </c>
+      <c r="E283" t="s">
+        <v>17</v>
+      </c>
+      <c r="F283" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G283" s="3">
+        <v>1.399</v>
+      </c>
+      <c r="H283" s="3">
+        <v>0</v>
+      </c>
+      <c r="I283" s="2">
+        <f t="shared" si="0"/>
+        <v>1.429</v>
+      </c>
+      <c r="O283" s="5">
+        <v>1230245380096</v>
+      </c>
+    </row>
+    <row r="284" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B284" t="s">
+        <v>5</v>
+      </c>
+      <c r="C284" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D284" t="s">
+        <v>476</v>
+      </c>
+      <c r="E284" t="s">
+        <v>22</v>
+      </c>
+      <c r="F284" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G284" s="3">
+        <v>1.359</v>
+      </c>
+      <c r="H284" s="3">
+        <v>0</v>
+      </c>
+      <c r="I284" s="2">
+        <f t="shared" si="0"/>
+        <v>1.389</v>
+      </c>
+      <c r="O284" s="5">
+        <v>1230245380096</v>
+      </c>
+    </row>
+    <row r="285" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B285" t="s">
+        <v>5</v>
+      </c>
+      <c r="C285" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D285" t="s">
+        <v>476</v>
+      </c>
+      <c r="E285" t="s">
+        <v>71</v>
+      </c>
+      <c r="F285" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G285" s="3">
+        <v>1.619</v>
+      </c>
+      <c r="H285" s="3">
+        <v>0</v>
+      </c>
+      <c r="I285" s="2">
+        <f t="shared" si="0"/>
+        <v>1.649</v>
+      </c>
+      <c r="O285" s="5">
+        <v>1230245380096</v>
       </c>
     </row>
   </sheetData>
